--- a/data/trans_orig/IP2005-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP2005-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>83453</t>
+          <t>83585</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>91805</t>
+          <t>91593</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77410</t>
+          <t>77354</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86458</t>
+          <t>86486</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>164348</t>
+          <t>163744</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>175859</t>
+          <t>176181</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,72%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3177</t>
+          <t>3389</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11529</t>
+          <t>11397</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4553</t>
+          <t>4525</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13601</t>
+          <t>13657</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10135</t>
+          <t>9813</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21646</t>
+          <t>22250</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,96%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68368</t>
+          <t>68339</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>76581</t>
+          <t>76953</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69672</t>
+          <t>69577</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78088</t>
+          <t>78311</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>141808</t>
+          <t>141543</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>153782</t>
+          <t>153058</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3799</t>
+          <t>3427</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12012</t>
+          <t>12041</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4297</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12713</t>
+          <t>12808</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>8983</t>
+          <t>9707</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20957</t>
+          <t>21222</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>52160</t>
+          <t>51811</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>60488</t>
+          <t>60352</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,1%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82565</t>
+          <t>83070</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92411</t>
+          <t>92452</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>138746</t>
+          <t>137974</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>151113</t>
+          <t>151228</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,52%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3396</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11724</t>
+          <t>12073</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>5369</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15256</t>
+          <t>14751</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10591</t>
+          <t>10476</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22958</t>
+          <t>23730</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,68%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>157932</t>
+          <t>158238</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>172988</t>
+          <t>172959</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>155308</t>
+          <t>155816</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>169687</t>
+          <t>169972</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,67%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>317178</t>
+          <t>318087</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>337981</t>
+          <t>338619</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>90,11%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>17194</t>
+          <t>17223</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>32250</t>
+          <t>31944</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15929</t>
+          <t>15644</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30308</t>
+          <t>29800</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37817</t>
+          <t>37179</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>58620</t>
+          <t>57711</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,36%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80280</t>
+          <t>80388</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>90444</t>
+          <t>90139</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>98807</t>
+          <t>98857</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>109949</t>
+          <t>110203</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>182841</t>
+          <t>182813</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>197572</t>
+          <t>197350</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>91,14%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6382</t>
+          <t>6687</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16546</t>
+          <t>16438</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9755</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20897</t>
+          <t>20847</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>18957</t>
+          <t>19179</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>33688</t>
+          <t>33716</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,57%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>63108</t>
+          <t>63293</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>69430</t>
+          <t>69425</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58326</t>
+          <t>58670</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64404</t>
+          <t>64390</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>124444</t>
+          <t>124353</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>132635</t>
+          <t>132642</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>91,62%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1320</t>
+          <t>1325</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7642</t>
+          <t>7457</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2581,7 +2581,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>690</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>6410</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3194</t>
+          <t>3187</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11385</t>
+          <t>11476</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,45%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>525365</t>
+          <t>527312</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>548793</t>
+          <t>549008</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>88,0%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>562666</t>
+          <t>564588</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>587800</t>
+          <t>588649</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1099831</t>
+          <t>1097409</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1132830</t>
+          <t>1131526</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>91,35%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>48212</t>
+          <t>47997</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>71640</t>
+          <t>69693</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>53816</t>
+          <t>52967</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>78950</t>
+          <t>77028</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>105790</t>
+          <t>107094</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>138789</t>
+          <t>141211</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>72497</t>
+          <t>72562</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80643</t>
+          <t>80504</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>87,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>73997</t>
+          <t>74064</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80770</t>
+          <t>81238</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>150607</t>
+          <t>150532</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>160766</t>
+          <t>160204</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,52%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2690</t>
+          <t>2829</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10836</t>
+          <t>10771</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1402</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8643</t>
+          <t>8576</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5208</t>
+          <t>5770</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15367</t>
+          <t>15442</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73199</t>
+          <t>73652</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82262</t>
+          <t>82467</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>86,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85005</t>
+          <t>84985</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>90821</t>
+          <t>90804</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>161606</t>
+          <t>162093</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>171976</t>
+          <t>172143</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>2801</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12069</t>
+          <t>11616</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>7089</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5366</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15736</t>
+          <t>15249</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65371</t>
+          <t>65451</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75453</t>
+          <t>75375</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>70080</t>
+          <t>70565</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78773</t>
+          <t>78845</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>139754</t>
+          <t>139155</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>152591</t>
+          <t>152238</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,11%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>5874</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15878</t>
+          <t>15798</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3487</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12180</t>
+          <t>11695</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10917</t>
+          <t>11270</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>23754</t>
+          <t>24353</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>163699</t>
+          <t>163258</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>177742</t>
+          <t>177380</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>85,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>188632</t>
+          <t>188260</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>200720</t>
+          <t>200783</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>357515</t>
+          <t>357140</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>375972</t>
+          <t>375274</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12603</t>
+          <t>12965</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26646</t>
+          <t>27087</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9902</t>
+          <t>9839</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21990</t>
+          <t>22362</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>24995</t>
+          <t>25693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>43827</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>112380</t>
+          <t>112049</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>125673</t>
+          <t>125919</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>102970</t>
+          <t>103640</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>116457</t>
+          <t>116608</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>220857</t>
+          <t>221165</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>240562</t>
+          <t>239287</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>89,87%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11699</t>
+          <t>11453</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24992</t>
+          <t>25323</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12443</t>
+          <t>12292</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25930</t>
+          <t>25260</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>25710</t>
+          <t>26985</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45415</t>
+          <t>45107</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>45844</t>
+          <t>45912</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53551</t>
+          <t>54109</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>62915</t>
+          <t>62615</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>80,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>102178</t>
+          <t>101837</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>111651</t>
+          <t>111877</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -5201,7 +5201,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>3987</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4584</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>13390</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5747</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>15220</t>
+          <t>15561</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>553550</t>
+          <t>554486</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>579708</t>
+          <t>579540</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>596588</t>
+          <t>595241</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>619023</t>
+          <t>619802</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1158544</t>
+          <t>1157177</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1193852</t>
+          <t>1190749</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,2%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>47759</t>
+          <t>47927</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>73917</t>
+          <t>72981</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>44971</t>
+          <t>44192</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>67406</t>
+          <t>68753</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>97609</t>
+          <t>100712</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>132917</t>
+          <t>134284</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67770</t>
+          <t>68754</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75826</t>
+          <t>75976</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>77510</t>
+          <t>77147</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86216</t>
+          <t>86516</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>85,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>149384</t>
+          <t>149649</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>160847</t>
+          <t>160739</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>89,24%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9484</t>
+          <t>8500</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12636</t>
+          <t>12999</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18017</t>
+          <t>17752</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88158</t>
+          <t>87741</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95132</t>
+          <t>95042</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>92244</t>
+          <t>92394</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>101753</t>
+          <t>101740</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>183677</t>
+          <t>183795</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>194979</t>
+          <t>195422</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8896</t>
+          <t>9313</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>3774</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13283</t>
+          <t>13133</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7602</t>
+          <t>7159</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18904</t>
+          <t>18786</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50728</t>
+          <t>50721</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>57178</t>
+          <t>57215</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61891</t>
+          <t>62161</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68679</t>
+          <t>68635</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>116121</t>
+          <t>115639</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>124695</t>
+          <t>124660</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>96,94%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1314</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7764</t>
+          <t>7771</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1430</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>7948</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>3906</t>
+          <t>3941</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>12480</t>
+          <t>12962</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,08%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>180118</t>
+          <t>180028</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>193423</t>
+          <t>193671</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>168709</t>
+          <t>169462</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>185058</t>
+          <t>184662</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>83,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>354800</t>
+          <t>355117</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>375714</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,92%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12810</t>
+          <t>12562</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26115</t>
+          <t>26205</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17377</t>
+          <t>17773</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33726</t>
+          <t>32973</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32954</t>
+          <t>33024</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>53868</t>
+          <t>53551</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>116166</t>
+          <t>116247</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>125728</t>
+          <t>125895</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>88,82%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>113978</t>
+          <t>113845</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>125891</t>
+          <t>125528</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>234053</t>
+          <t>234725</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>249476</t>
+          <t>249313</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,0%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5066</t>
+          <t>4899</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14628</t>
+          <t>14547</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,18%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8550</t>
+          <t>8913</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20463</t>
+          <t>20596</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15759</t>
+          <t>15922</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>31182</t>
+          <t>30510</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>48812</t>
+          <t>49089</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>55379</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>58511</t>
+          <t>58259</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>64341</t>
+          <t>64340</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>109240</t>
+          <t>110057</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>118482</t>
+          <t>118452</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>90,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1369</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>7864</t>
+          <t>7587</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>674</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6503</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3238</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>12450</t>
+          <t>11633</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>571292</t>
+          <t>571491</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>593065</t>
+          <t>592735</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>594507</t>
+          <t>594794</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>620705</t>
+          <t>620061</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,97%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1173875</t>
+          <t>1173638</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1207586</t>
+          <t>1205787</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>33437</t>
+          <t>33767</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>55210</t>
+          <t>55011</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>46967</t>
+          <t>47611</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>73165</t>
+          <t>72878</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>86589</t>
+          <t>88388</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>120300</t>
+          <t>120537</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>80188</t>
+          <t>79652</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92364</t>
+          <t>92062</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>113811</t>
+          <t>113802</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>126192</t>
+          <t>126018</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>197980</t>
+          <t>197242</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>215487</t>
+          <t>215363</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>82,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,23%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10896</t>
+          <t>11198</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23072</t>
+          <t>23608</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9218</t>
+          <t>9392</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21599</t>
+          <t>21608</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>23183</t>
+          <t>23307</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>40690</t>
+          <t>41428</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>17,36%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>73578</t>
+          <t>73295</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>85198</t>
+          <t>85290</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74361</t>
+          <t>74981</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>85956</t>
+          <t>86060</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>153531</t>
+          <t>152864</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>168438</t>
+          <t>168795</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,82%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9483</t>
+          <t>9391</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21103</t>
+          <t>21386</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>7186</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18885</t>
+          <t>18265</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19489</t>
+          <t>19132</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>34396</t>
+          <t>35063</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,66%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41214</t>
+          <t>41317</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>48053</t>
+          <t>47928</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49117</t>
+          <t>49018</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>59536</t>
+          <t>59550</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>77,79%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>93134</t>
+          <t>93913</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>105540</t>
+          <t>105636</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,43%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8711</t>
+          <t>8608</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3601</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14020</t>
+          <t>14119</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7522</t>
+          <t>7426</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>19149</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>16,94%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>182121</t>
+          <t>182583</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>201227</t>
+          <t>200639</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>85,12%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>173842</t>
+          <t>173483</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>192665</t>
+          <t>192186</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,77%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>360944</t>
+          <t>362654</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>387539</t>
+          <t>388990</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,19%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12739</t>
+          <t>13327</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31845</t>
+          <t>31383</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19941</t>
+          <t>20420</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>38764</t>
+          <t>39123</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,23%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39033</t>
+          <t>37582</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>65628</t>
+          <t>63918</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>96920</t>
+          <t>96530</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>108661</t>
+          <t>108730</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,28%</t>
+          <t>81,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>135778</t>
+          <t>136185</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>151676</t>
+          <t>151056</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>238541</t>
+          <t>237997</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>256947</t>
+          <t>256355</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,44%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9126</t>
+          <t>9057</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>20867</t>
+          <t>21257</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>7864</t>
+          <t>8484</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23762</t>
+          <t>23355</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>20379</t>
+          <t>20971</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>38785</t>
+          <t>39329</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57608</t>
+          <t>56877</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>65815</t>
+          <t>65941</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>55681</t>
+          <t>56203</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>66361</t>
+          <t>66439</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>79,03%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>117362</t>
+          <t>117281</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>130619</t>
+          <t>130449</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,61%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3080</t>
+          <t>2954</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>11287</t>
+          <t>12018</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4015</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>14773</t>
+          <t>14251</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8730</t>
+          <t>8900</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21987</t>
+          <t>22068</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,84%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>552801</t>
+          <t>553416</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>583490</t>
+          <t>583996</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>631644</t>
+          <t>630183</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>663992</t>
+          <t>663054</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1197054</t>
+          <t>1196503</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1241161</t>
+          <t>1242960</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>89,75%</t>
+          <t>89,88%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>65023</t>
+          <t>64517</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>95712</t>
+          <t>95097</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>70401</t>
+          <t>71339</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>102749</t>
+          <t>104210</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>141746</t>
+          <t>139947</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>185853</t>
+          <t>186404</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
